--- a/output/pdf_financials_xlsx/RES.xlsx
+++ b/output/pdf_financials_xlsx/RES.xlsx
@@ -1057,10 +1057,10 @@
         <v>-0.07724499999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
         <v>-0.07724499999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         <v>-0.07724499999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>-0.07724499999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1667,10 +1667,10 @@
         <v>-0.07724499999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -4308,37 +4308,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.048121</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.048121</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.108121</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.108121</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.118975</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.118975</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.118975</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.118975</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.118975</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.25683</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.073127</v>
+        <v>0.347003</v>
       </c>
     </row>
     <row r="93">
@@ -5390,10 +5390,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.116728</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>-0.357442</v>
+        <v>-0.373056</v>
       </c>
     </row>
     <row r="119">
@@ -7119,7 +7119,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7186,7 +7190,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7894,7 +7902,11 @@
           <t>Share-based payment reserve 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8762,7 +8774,11 @@
           <t>Share‐based payment reserve (Note 5) 45,848</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9571,7 +9587,11 @@
           <t>Share-based payment reserve (Note 5) 45,848</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -10222,7 +10242,11 @@
           <t>Share-based payment reserve (note 4)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -10855,7 +10879,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.034994</v>
       </c>
@@ -11200,7 +11228,11 @@
           <t>Warrant Reserve (note 4(d))</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.013127</v>
       </c>
@@ -11835,7 +11867,11 @@
           <t>Exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18721,10 +18757,10 @@
         </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>0.091437</v>
+        <v>-0.091437</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>0.120103</v>
+        <v>-0.120103</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RES.xlsx
+++ b/output/pdf_financials_xlsx/RES.xlsx
@@ -1870,37 +1870,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.391565</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.55759</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.49467</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.4354</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.05458</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.9448220000000001</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.81708</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.849176</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>2.061272</v>
+        <v>1.647278</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.056767</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.225651</v>
       </c>
     </row>
     <row r="35">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.391565</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.55759</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.49467</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.4354</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.05458</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.9448220000000001</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.81708</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.849176</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.061272</v>
+        <v>1.647278</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.056767</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.225651</v>
       </c>
     </row>
     <row r="37">
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.062457</v>
+        <v>0.00569</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.240313</v>
+        <v>0.014662</v>
       </c>
     </row>
     <row r="49">
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026677</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040667</v>
       </c>
     </row>
     <row r="125">
@@ -5696,10 +5696,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026677</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040667</v>
       </c>
     </row>
     <row r="126">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -12088,7 +12088,11 @@
           <t>Lease payments $</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RES.xlsx
+++ b/output/pdf_financials_xlsx/RES.xlsx
@@ -594,10 +594,8 @@
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
@@ -684,10 +682,8 @@
       <c r="G7" s="3" t="n">
         <v>0.055786</v>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H7" s="3" t="n">
+        <v>0.040409</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.055905</v>
@@ -726,10 +722,8 @@
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -768,10 +762,8 @@
       <c r="G9" s="3" t="n">
         <v>0.019309</v>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H9" s="3" t="n">
+        <v>0.019275</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.027878</v>
@@ -810,10 +802,8 @@
       <c r="G10" s="3" t="n">
         <v>0.075095</v>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H10" s="3" t="n">
+        <v>0.059684</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.083783</v>
@@ -894,10 +884,8 @@
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H12" s="3" t="n">
+        <v>0.00106</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -936,10 +924,8 @@
       <c r="G13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -978,10 +964,8 @@
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -1020,10 +1004,8 @@
       <c r="G15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1104,10 +1086,8 @@
       <c r="G17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1312,10 +1292,8 @@
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -1354,10 +1332,8 @@
       <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -1630,10 +1606,8 @@
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -4622,10 +4596,8 @@
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0</v>
@@ -4647,10 +4619,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005443</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004491</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -4664,10 +4636,8 @@
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>-0.024377</v>
@@ -4706,10 +4676,8 @@
       <c r="G102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>0</v>
@@ -4748,10 +4716,8 @@
       <c r="G103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0</v>
@@ -4790,10 +4756,8 @@
       <c r="G104" s="3" t="n">
         <v>0.010345</v>
       </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H104" s="3" t="n">
+        <v>-0.039686</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>0.00635</v>
@@ -4832,10 +4796,8 @@
       <c r="G105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>0</v>
@@ -4857,10 +4819,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.031407</v>
+        <v>-0.03685</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.004306</v>
+        <v>-0.000185</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.004172</v>
@@ -4874,10 +4836,8 @@
       <c r="G106" s="3" t="n">
         <v>0.010345</v>
       </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H106" s="3" t="n">
+        <v>-0.039686</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-0.018027</v>
@@ -4916,10 +4876,8 @@
       <c r="G107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>0</v>
@@ -4958,10 +4916,8 @@
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>0</v>
@@ -5000,10 +4956,8 @@
       <c r="G109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>0</v>
@@ -5042,10 +4996,8 @@
       <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5084,10 +5036,8 @@
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -5126,10 +5076,8 @@
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -5168,10 +5116,8 @@
       <c r="G113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>0</v>
@@ -5210,10 +5156,8 @@
       <c r="G114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -5252,10 +5196,8 @@
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -5294,10 +5236,8 @@
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -5336,10 +5276,8 @@
       <c r="G117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>0</v>
@@ -5378,10 +5316,8 @@
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -5474,10 +5410,8 @@
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -5516,10 +5450,8 @@
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>0</v>
@@ -5558,10 +5490,8 @@
       <c r="G122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>0</v>
@@ -5600,10 +5530,8 @@
       <c r="G123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>0</v>
@@ -5642,10 +5570,8 @@
       <c r="G124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -5684,10 +5610,8 @@
       <c r="G125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -5726,10 +5650,8 @@
       <c r="G126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>0</v>
@@ -5830,10 +5752,8 @@
       <c r="G128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
@@ -5926,10 +5846,8 @@
       <c r="G130" s="3" t="n">
         <v>1.05458</v>
       </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H130" s="3" t="n">
+        <v>0.9448220000000001</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>2.061272</v>
@@ -5968,10 +5886,8 @@
       <c r="G131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>0</v>
@@ -6010,10 +5926,8 @@
       <c r="G132" s="3" t="n">
         <v>-0.109758</v>
       </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H132" s="3" t="n">
+        <v>-0.127742</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>-0.212096</v>
@@ -6052,10 +5966,8 @@
       <c r="G133" s="3" t="n">
         <v>0.9448220000000001</v>
       </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H133" s="3" t="n">
+        <v>0.81708</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>1.849176</v>
@@ -6094,10 +6006,8 @@
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -6165,7 +6075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O198"/>
+  <dimension ref="A1:O236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13283,21 +13193,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>For the Years Ended December</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -13318,26 +13220,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="5" t="n">
-        <v>-0.091437</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>-0.120103</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M100" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -13358,19 +13260,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Net loss $ (194,069) $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -13391,8 +13289,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="5" t="n">
-        <v>0.010854</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -13409,10 +13309,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M101" s="5" t="n">
+        <v>-0.133494</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -13433,12 +13331,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Amounts receivable                                               (24,377)                       ‐</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Accounts payable and accrued liabilities (6,350)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13466,11 +13364,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="5" t="n">
-        <v>-0.003787</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.010345</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -13482,10 +13384,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M102" s="5" t="n">
+        <v>0.008758999999999999</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -13506,19 +13406,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Amounts receivable                                               (24,377)                       ‐</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash used in operating activities (212,096)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -13539,11 +13435,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="5" t="n">
-        <v>-0.08437</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>-0.109758</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -13555,10 +13455,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M103" s="5" t="n">
+        <v>-0.124735</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -13579,17 +13477,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Proceeds from private placement, net of share issue costs</t>
+          <t>Proceeds from issuance of common shares ‐</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -13612,8 +13510,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="5" t="n">
-        <v>0.70355</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -13630,10 +13530,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M104" s="5" t="n">
+        <v>1.5</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -13654,12 +13552,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activity</t>
+          <t>Change in cash and cash equivalents for the year (212,096)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -13683,8 +13581,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="5" t="n">
-        <v>0.70355</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -13701,10 +13601,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M105" s="5" t="n">
+        <v>1.375265</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -13725,17 +13623,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Cash and cash equivalents, beginning of the year 2,061,272</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -13758,11 +13656,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="5" t="n">
-        <v>0.61918</v>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>-0.109758</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -13774,10 +13676,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M106" s="5" t="n">
+        <v>0.686007</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -13798,17 +13698,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Cash and cash equivalents, end of the year $ 1,849,176 $</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13831,11 +13731,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="5" t="n">
-        <v>0.4354</v>
-      </c>
-      <c r="J107" s="5" t="n">
-        <v>1.05458</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -13847,10 +13751,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M107" s="5" t="n">
+        <v>2.061272</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -13871,19 +13773,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financing activity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Net loss $ (131,321) $</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -13904,16 +13802,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="5" t="n">
-        <v>1.05458</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0.9448220000000001</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>-0.087031</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -13944,30 +13844,34 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>-0.118103</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>-0.096648</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>-0.067092</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>-0.07724499999999999</v>
+          <t>Amounts receivable (6,062)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -13979,10 +13883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K109" s="5" t="n">
+        <v>-0.001025</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -14013,17 +13915,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities 6,310</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -14036,11 +13938,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" s="5" t="n">
-        <v>-7.7e-05</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0.001649</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -14052,10 +13958,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K110" s="5" t="n">
+        <v>-0.039686</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -14086,19 +13990,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Trade accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Cash used in operating activities (131,073)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -14109,11 +14009,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" s="5" t="n">
-        <v>0.004249</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>0.016326</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -14125,10 +14029,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K111" s="5" t="n">
+        <v>-0.127742</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -14159,19 +14061,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents for the year (131,073)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -14182,11 +14080,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" s="5" t="n">
-        <v>-0.06292</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>-0.05927</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -14198,10 +14100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K112" s="5" t="n">
+        <v>-0.127742</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -14232,17 +14132,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
+          <t>Cash and cash equivalents, beginning of the year 817,080</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -14255,11 +14155,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="5" t="n">
-        <v>-0.06292</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>-0.05927</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -14271,10 +14175,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K113" s="5" t="n">
+        <v>0.9448220000000001</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -14305,17 +14207,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash and cash equivalents, end of the year $ 686,007 $</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -14328,11 +14230,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G114" s="5" t="n">
-        <v>0.55759</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>0.49467</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -14344,10 +14250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K114" s="5" t="n">
+        <v>0.81708</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -14378,17 +14282,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Supplemental information</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Interest paid $ - $</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -14401,11 +14305,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="5" t="n">
-        <v>0.49467</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>0.4354</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -14451,20 +14359,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Write off of GST receivable                                            17,683.                       -.</t>
+          <t>Supplemental information</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>Taxes paid $ - $</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>-0.005443</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-0.004491</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14520,24 +14432,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Write off of GST receivable                                            17,683.                       -.</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>-0.001372</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.0002</v>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -14549,15 +14465,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>-0.091437</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>-0.120103</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -14593,24 +14505,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Write off of GST receivable                                            17,683.                       -.</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Trade accounts payable and accrued liabilities</t>
+          <t>Share based compensation</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>-0.030035</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.004506</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -14622,10 +14538,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="5" t="n">
+        <v>0.010854</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -14666,24 +14580,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Write off of GST receivable                                            17,683.                       -.</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>-0.119959</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>-0.07915</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -14695,15 +14613,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="5" t="n">
+        <v>-0.003787</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0.010345</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -14739,24 +14653,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
+          <t>Net cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0.25</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -14768,15 +14686,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="5" t="n">
+        <v>-0.08437</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>-0.109758</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -14812,12 +14726,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Share issuances, net of share issue costs (note 4(b))</t>
+          <t>Proceeds from private placement, net of share issue costs</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14825,11 +14739,15 @@
           <t>NetOtherFinancingCharges</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
-        <v>-0.010878</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>-0.004825</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -14841,10 +14759,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="5" t="n">
+        <v>0.70355</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -14885,24 +14801,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>0.239122</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.245175</v>
+          <t>Net cash flows provided by financing activity</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -14914,10 +14830,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="5" t="n">
+        <v>0.70355</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -14958,12 +14872,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -14971,11 +14885,15 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E123" s="5" t="n">
-        <v>0.119163</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.166025</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -14987,15 +14905,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="5" t="n">
+        <v>0.61918</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>-0.109758</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -15031,12 +14945,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15044,11 +14958,15 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>0.272402</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>0.391565</v>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -15060,15 +14978,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="5" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>1.05458</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -15104,12 +15018,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash, end of the year $</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15117,11 +15031,15 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
-        <v>0.391565</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.55759</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -15133,15 +15051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="5" t="n">
+        <v>1.05458</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>0.9448220000000001</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -15172,35 +15086,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Notes December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>-0.118103</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.096648</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>-0.067092</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-0.07724499999999999</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -15227,32 +15141,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N126" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="O126" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Office $</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -15265,15 +15183,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G127" s="5" t="n">
+        <v>-7.7e-05</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0.001649</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -15300,32 +15214,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N127" s="5" t="n">
-        <v>0.064481</v>
-      </c>
-      <c r="O127" s="5" t="n">
-        <v>0.052756</v>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
+          <t>Trade accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SellingAndMarketingExpense</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -15338,15 +15256,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="5" t="n">
+        <v>0.004249</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.016326</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -15373,8 +15287,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N128" s="5" t="n">
-        <v>0.0013</v>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -15385,22 +15301,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -15413,15 +15329,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="5" t="n">
+        <v>-0.06292</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>-0.05927</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -15448,32 +15360,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N129" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O129" s="5" t="n">
-        <v>0.2145</v>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Decrease in cash</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -15486,15 +15402,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="5" t="n">
+        <v>-0.06292</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>-0.05927</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -15521,32 +15433,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N130" s="5" t="n">
-        <v>0.020868</v>
-      </c>
-      <c r="O130" s="5" t="n">
-        <v>0.031302</v>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Professional fees 10</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -15559,15 +15475,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="5" t="n">
+        <v>0.55759</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.49467</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -15589,35 +15501,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M131" s="5" t="n">
-        <v>0.170686</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>0.106547</v>
-      </c>
-      <c r="O131" s="5" t="n">
-        <v>0.106985</v>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -15630,15 +15548,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="5" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.4354</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -15665,43 +15579,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N132" s="5" t="n">
-        <v>0.00694</v>
-      </c>
-      <c r="O132" s="5" t="n">
-        <v>0.018005</v>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Write off of GST receivable                                            17,683.                       -.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.005443</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>-0.004491</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -15728,45 +15642,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L133" s="5" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v>0.019404</v>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v>0.038689</v>
-      </c>
-      <c r="O133" s="5" t="n">
-        <v>0.03124</v>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Write off of GST receivable                                            17,683.                       -.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Total general and administration expenses $</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.001372</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>-0.0002</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -15803,43 +15725,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N134" s="5" t="n">
-        <v>0.418825</v>
-      </c>
-      <c r="O134" s="5" t="n">
-        <v>0.454788</v>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Write off of GST receivable                                            17,683.                       -.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Operating loss $</t>
+          <t>Trade accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>-0.030035</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0.004506</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -15876,39 +15798,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N135" s="5" t="n">
-        <v>-0.418825</v>
-      </c>
-      <c r="O135" s="5" t="n">
-        <v>-0.454788</v>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Write off of GST receivable                                            17,683.                       -.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Due diligence</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>-0.119959</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-0.07915</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -15950,36 +15876,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O136" s="5" t="n">
-        <v>-0.074591</v>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Finance cost 7</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of shares</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -16016,39 +15944,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N137" s="5" t="n">
-        <v>-0.011537</v>
-      </c>
-      <c r="O137" s="5" t="n">
-        <v>-0.014251</v>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Total other expenses $</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuances, net of share issue costs (note 4(b))</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-0.010878</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.004825</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -16085,43 +16017,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N138" s="5" t="n">
-        <v>-0.011537</v>
-      </c>
-      <c r="O138" s="5" t="n">
-        <v>-0.088842</v>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.239122</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.245175</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -16153,42 +16085,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M139" s="5" t="n">
-        <v>-0.247173</v>
-      </c>
-      <c r="N139" s="5" t="n">
-        <v>-0.430362</v>
-      </c>
-      <c r="O139" s="5" t="n">
-        <v>-0.5436299999999999</v>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loss per share attributable to shareholders – basic and</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.119163</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.166025</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -16225,39 +16163,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N140" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding total</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.272402</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0.391565</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -16294,39 +16236,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N141" s="5" t="n">
-        <v>24.214355</v>
-      </c>
-      <c r="O141" s="5" t="n">
-        <v>28.665607</v>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Notes        shares</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Balance - January 1, 2024 22,520,367 2,888,720 45,848 – 73,127</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.391565</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.55759</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -16363,11 +16309,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N142" s="5" t="n">
-        <v>1.60421</v>
-      </c>
-      <c r="O142" s="5" t="n">
-        <v>-1.403485</v>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -16376,14 +16326,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Consideration units issued to acquire</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Consideration units issued to acquire</t>
+          <t>Notes December 31, 2025 December</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -16433,12 +16379,10 @@
         </is>
       </c>
       <c r="N143" s="5" t="n">
-        <v>0.447855</v>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="O143" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="144">
@@ -16449,17 +16393,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>mineral property rights</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net loss for the year – – – – –</t>
+          <t>Office $</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16508,10 +16452,10 @@
         </is>
       </c>
       <c r="N144" s="5" t="n">
-        <v>-0.430362</v>
+        <v>0.064481</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>-0.430362</v>
+        <v>0.052756</v>
       </c>
     </row>
     <row r="145">
@@ -16522,15 +16466,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mineral property rights</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 24,457,867 3,198,720 45,848 137,855 73,127</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Sales and marketing</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -16577,10 +16525,12 @@
         </is>
       </c>
       <c r="N145" s="5" t="n">
-        <v>1.621703</v>
-      </c>
-      <c r="O145" s="5" t="n">
-        <v>-1.833847</v>
+        <v>0.0013</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -16591,15 +16541,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Common shares issued to acquire</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Common shares issued to acquire</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Management fees 10</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -16646,12 +16600,10 @@
         </is>
       </c>
       <c r="N146" s="5" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.18</v>
+      </c>
+      <c r="O146" s="5" t="n">
+        <v>0.2145</v>
       </c>
     </row>
     <row r="147">
@@ -16662,17 +16614,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1000334153 Ontario Inc.</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net loss for the year – – – –</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -16721,10 +16673,10 @@
         </is>
       </c>
       <c r="N147" s="5" t="n">
-        <v>-0.5436299999999999</v>
+        <v>0.020868</v>
       </c>
       <c r="O147" s="5" t="n">
-        <v>-0.5436299999999999</v>
+        <v>0.031302</v>
       </c>
     </row>
     <row r="148">
@@ -16735,15 +16687,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1000334153 Ontario Inc.</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2025 43,095,367 4,256,533 45,848 228,028 73,127</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Professional fees 10</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -16784,16 +16740,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M148" s="5" t="n">
+        <v>0.170686</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>2.226059</v>
+        <v>0.106547</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>-2.377477</v>
+        <v>0.106985</v>
       </c>
     </row>
     <row r="149">
@@ -16809,10 +16763,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bad debt $</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -16853,18 +16811,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M149" s="5" t="n">
-        <v>0.007088</v>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="O149" s="5" t="n">
+        <v>0.018005</v>
       </c>
     </row>
     <row r="150">
@@ -16880,7 +16836,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16923,23 +16879,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L150" s="5" t="n">
+        <v>0.0384</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>0.009623</v>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019404</v>
+      </c>
+      <c r="N150" s="5" t="n">
+        <v>0.038689</v>
+      </c>
+      <c r="O150" s="5" t="n">
+        <v>0.03124</v>
       </c>
     </row>
     <row r="151">
@@ -16955,14 +16905,10 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Total general and administration expenses $</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -16998,19 +16944,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L151" s="5" t="n">
-        <v>0.027878</v>
-      </c>
-      <c r="M151" s="5" t="n">
-        <v>0.040372</v>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N151" s="5" t="n">
-        <v>0.064481</v>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.418825</v>
+      </c>
+      <c r="O151" s="5" t="n">
+        <v>0.454788</v>
       </c>
     </row>
     <row r="152">
@@ -17026,10 +16974,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Total expenses before other item noted below</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Operating loss $</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -17070,16 +17022,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M152" s="5" t="n">
-        <v>0.247173</v>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N152" s="5" t="n">
-        <v>0.418825</v>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.418825</v>
+      </c>
+      <c r="O152" s="5" t="n">
+        <v>-0.454788</v>
       </c>
     </row>
     <row r="153">
@@ -17095,14 +17047,10 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Loss per share attributable to shareholders – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Due diligence</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -17143,16 +17091,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M153" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N153" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" s="5" t="n">
+        <v>-0.074591</v>
       </c>
     </row>
     <row r="154">
@@ -17163,12 +17113,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Balance at January 1, 2023 $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
+          <t>Finance cost 7</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -17212,16 +17162,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M154" s="5" t="n">
-        <v>1.851383</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N154" s="5" t="n">
-        <v>-1.156312</v>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.011537</v>
+      </c>
+      <c r="O154" s="5" t="n">
+        <v>-0.014251</v>
       </c>
     </row>
     <row r="155">
@@ -17232,19 +17182,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Net loss - - - -</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Total other expenses $</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -17285,16 +17231,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M155" s="5" t="n">
-        <v>-0.247173</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N155" s="5" t="n">
-        <v>-0.247173</v>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.011537</v>
+      </c>
+      <c r="O155" s="5" t="n">
+        <v>-0.088842</v>
       </c>
     </row>
     <row r="156">
@@ -17305,15 +17251,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -17355,15 +17305,13 @@
         </is>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.60421</v>
+        <v>-0.247173</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>-1.403485</v>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.430362</v>
+      </c>
+      <c r="O156" s="5" t="n">
+        <v>-0.5436299999999999</v>
       </c>
     </row>
     <row r="157">
@@ -17374,12 +17322,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Balance at January 1, 2024 $ $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
+          <t>Loss per share attributable to shareholders – basic and</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -17423,16 +17371,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M157" s="5" t="n">
-        <v>1.60421</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N157" s="5" t="n">
-        <v>-1.403485</v>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="O157" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="158">
@@ -17443,12 +17391,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Consideration units issued to 6,8,9 acquire mineral property rights 310,000 - 137,855 -</t>
+          <t>Weighted average number of common shares outstanding total</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -17492,18 +17440,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M158" s="5" t="n">
-        <v>0.447855</v>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="n">
+        <v>24.214355</v>
+      </c>
+      <c r="O158" s="5" t="n">
+        <v>28.665607</v>
       </c>
     </row>
     <row r="159">
@@ -17514,12 +17460,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
+          <t>Notes        shares</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 $ 3,198,720 $ 45,848 $ 137,855 $ 73,127 $</t>
+          <t>Balance - January 1, 2024 22,520,367 2,888,720 45,848 – 73,127</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -17563,16 +17509,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M159" s="5" t="n">
-        <v>1.621703</v>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N159" s="5" t="n">
-        <v>-1.833847</v>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.60421</v>
+      </c>
+      <c r="O159" s="5" t="n">
+        <v>-1.403485</v>
       </c>
     </row>
     <row r="160">
@@ -17583,19 +17529,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Consideration units issued to acquire</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Consideration units issued to acquire</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -17631,16 +17573,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L160" s="5" t="n">
-        <v>0.017505</v>
-      </c>
-      <c r="M160" s="5" t="n">
-        <v>0.009623</v>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="n">
+        <v>0.447855</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -17656,15 +17600,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>mineral property rights</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bad debt</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Net loss for the year – – – – –</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -17705,18 +17653,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M161" s="5" t="n">
-        <v>0.007088</v>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="n">
+        <v>-0.430362</v>
+      </c>
+      <c r="O161" s="5" t="n">
+        <v>-0.430362</v>
       </c>
     </row>
     <row r="162">
@@ -17727,19 +17673,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>mineral property rights</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2024 24,457,867 3,198,720 45,848 137,855 73,127</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -17775,21 +17717,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L162" s="5" t="n">
-        <v>0.110286</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>0.170686</v>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="n">
+        <v>1.621703</v>
+      </c>
+      <c r="O162" s="5" t="n">
+        <v>-1.833847</v>
       </c>
     </row>
     <row r="163">
@@ -17800,12 +17742,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Common shares issued to acquire</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Total general and administration expenses</t>
+          <t>Common shares issued to acquire</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -17844,16 +17786,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L163" s="5" t="n">
-        <v>0.194069</v>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v>0.247173</v>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="5" t="n">
+        <v>0.835</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -17869,17 +17813,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>1000334153 Ontario Inc.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Operating loss</t>
+          <t>Net loss for the year – – – –</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -17917,21 +17861,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L164" s="5" t="n">
-        <v>-0.194069</v>
-      </c>
-      <c r="M164" s="5" t="n">
-        <v>-0.247173</v>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="5" t="n">
+        <v>-0.5436299999999999</v>
+      </c>
+      <c r="O164" s="5" t="n">
+        <v>-0.5436299999999999</v>
       </c>
     </row>
     <row r="165">
@@ -17942,19 +17886,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>1000334153 Ontario Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2025 43,095,367 4,256,533 45,848 228,028 73,127</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -17990,21 +17930,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L165" s="5" t="n">
-        <v>-0.194069</v>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v>-0.247173</v>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="5" t="n">
+        <v>2.226059</v>
+      </c>
+      <c r="O165" s="5" t="n">
+        <v>-2.377477</v>
       </c>
     </row>
     <row r="166">
@@ -18015,12 +17955,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Balance - January 1, 2022 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
+          <t>Bad debt $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -18059,11 +17999,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L166" s="5" t="n">
-        <v>2.045452</v>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" s="5" t="n">
-        <v>-0.962243</v>
+        <v>0.007088</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -18084,17 +18026,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Net loss - - - -</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -18132,11 +18074,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L167" s="5" t="n">
-        <v>-0.194069</v>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="5" t="n">
-        <v>-0.194069</v>
+        <v>0.009623</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -18157,15 +18101,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 5 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -18202,15 +18150,13 @@
         </is>
       </c>
       <c r="L168" s="5" t="n">
-        <v>1.851383</v>
+        <v>0.027878</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>-1.156312</v>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.040372</v>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>0.064481</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -18226,12 +18172,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Balance - January 1, 2023 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
+          <t>Total expenses before other item noted below</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -18270,16 +18216,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L169" s="5" t="n">
-        <v>1.851383</v>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="5" t="n">
-        <v>-1.156312</v>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247173</v>
+      </c>
+      <c r="N169" s="5" t="n">
+        <v>0.418825</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -18295,15 +18241,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 5 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Loss per share attributable to shareholders – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -18339,16 +18289,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L170" s="5" t="n">
-        <v>1.60421</v>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M170" s="5" t="n">
-        <v>-1.403485</v>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="N170" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -18364,19 +18314,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Consulting fees (note 5) $</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance at January 1, 2023 $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -18397,11 +18343,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="5" t="n">
-        <v>0.01575</v>
-      </c>
-      <c r="J171" s="5" t="n">
-        <v>0.0315</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -18413,15 +18363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M171" s="5" t="n">
+        <v>1.851383</v>
+      </c>
+      <c r="N171" s="5" t="n">
+        <v>-1.156312</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -18437,17 +18383,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Net loss - - - -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -18470,11 +18416,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n">
-        <v>0.006658</v>
-      </c>
-      <c r="J172" s="5" t="n">
-        <v>0.019309</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -18486,15 +18436,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M172" s="5" t="n">
+        <v>-0.247173</v>
+      </c>
+      <c r="N172" s="5" t="n">
+        <v>-0.247173</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -18510,19 +18456,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2023 $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -18543,11 +18485,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="5" t="n">
-        <v>0.035361</v>
-      </c>
-      <c r="J173" s="5" t="n">
-        <v>0.045008</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -18559,15 +18505,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M173" s="5" t="n">
+        <v>1.60421</v>
+      </c>
+      <c r="N173" s="5" t="n">
+        <v>-1.403485</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -18583,12 +18525,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Share based compensation (note 4, 5)</t>
+          <t>Balance at January 1, 2024 $ $ 2,888,720 $ 45,848 $ - $ 73,127 $</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -18612,8 +18554,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" s="5" t="n">
-        <v>0.010854</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -18630,15 +18574,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M174" s="5" t="n">
+        <v>1.60421</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>-1.403485</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -18654,19 +18594,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Consideration units issued to 6,8,9 acquire mineral property rights 310,000 - 137,855 -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -18687,11 +18623,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I175" s="5" t="n">
-        <v>0.022814</v>
-      </c>
-      <c r="J175" s="5" t="n">
-        <v>0.024286</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -18703,10 +18643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M175" s="5" t="n">
+        <v>0.447855</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -18727,19 +18665,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Notes       Share capital            reserve            reserve            surplus                Deficit                Total</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2024 $ 3,198,720 $ 45,848 $ 137,855 $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -18760,11 +18694,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I176" s="5" t="n">
-        <v>-0.091437</v>
-      </c>
-      <c r="J176" s="5" t="n">
-        <v>-0.120103</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -18776,15 +18714,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M176" s="5" t="n">
+        <v>1.621703</v>
+      </c>
+      <c r="N176" s="5" t="n">
+        <v>-1.833847</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -18800,17 +18734,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Consulting fees $</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -18833,26 +18767,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="5" t="n">
-        <v>0</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L177" s="5" t="n">
+        <v>0.017505</v>
+      </c>
+      <c r="M177" s="5" t="n">
+        <v>0.009623</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -18873,19 +18807,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Bad debt</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -18906,11 +18836,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n">
-        <v>25.429637</v>
-      </c>
-      <c r="J178" s="5" t="n">
-        <v>31.931007</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -18922,10 +18856,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M178" s="5" t="n">
+        <v>0.007088</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -18946,30 +18878,38 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="n">
-        <v>0.00975</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="G179" s="5" t="n">
-        <v>0.00987</v>
-      </c>
-      <c r="H179" s="5" t="n">
-        <v>0.009344999999999999</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -18986,15 +18926,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L179" s="5" t="n">
+        <v>0.110286</v>
+      </c>
+      <c r="M179" s="5" t="n">
+        <v>0.170686</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -19015,30 +18951,34 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>0.0007159999999999999</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>0.000632</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>0.002821</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>0.001053</v>
+          <t>Total general and administration expenses</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -19055,15 +18995,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L180" s="5" t="n">
+        <v>0.194069</v>
+      </c>
+      <c r="M180" s="5" t="n">
+        <v>0.247173</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -19084,17 +19020,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -19107,11 +19043,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G181" s="5" t="n">
-        <v>0.019824</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0.014517</v>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -19128,15 +19068,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L181" s="5" t="n">
+        <v>-0.194069</v>
+      </c>
+      <c r="M181" s="5" t="n">
+        <v>-0.247173</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -19157,17 +19093,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>General and administration expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Net and comprehensive loss $</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -19180,11 +19116,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G182" s="5" t="n">
-        <v>0.019751</v>
-      </c>
-      <c r="H182" s="5" t="n">
-        <v>0.020753</v>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -19201,15 +19141,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L182" s="5" t="n">
+        <v>-0.194069</v>
+      </c>
+      <c r="M182" s="5" t="n">
+        <v>-0.247173</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -19230,19 +19166,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance - January 1, 2022 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -19253,11 +19185,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" s="5" t="n">
-        <v>0.014826</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>0.014909</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -19274,15 +19210,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L183" s="5" t="n">
+        <v>2.045452</v>
+      </c>
+      <c r="M183" s="5" t="n">
+        <v>-0.962243</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -19303,12 +19235,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Travel expense                                                      16,668.                       -.</t>
+          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Net loss - - - -</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -19326,11 +19258,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G184" s="5" t="n">
-        <v>-0.067092</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>-0.07724499999999999</v>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -19347,15 +19283,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L184" s="5" t="n">
+        <v>-0.194069</v>
+      </c>
+      <c r="M184" s="5" t="n">
+        <v>-0.194069</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
@@ -19376,30 +19308,34 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per share</t>
+          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G185" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>-1e-08</v>
+          <t>Balance at December 31, 2022 5 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -19416,15 +19352,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L185" s="5" t="n">
+        <v>1.851383</v>
+      </c>
+      <c r="M185" s="5" t="n">
+        <v>-1.156312</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -19445,30 +19377,34 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per share</t>
+          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="n">
-        <v>6.152055</v>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>8.110958999999999</v>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>11.664384</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>10.7</v>
+          <t>Balance - January 1, 2023 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -19485,15 +19421,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L186" s="5" t="n">
+        <v>1.851383</v>
+      </c>
+      <c r="M186" s="5" t="n">
+        <v>-1.156312</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -19514,12 +19446,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Shares          capital.           reserve.        surplus        reserve           Deficit.         Total</t>
+          <t>Notes       Shares            capital          Surplus          Surplus              Deficit             Total</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2014 11,700,000. $ 745,170. $ 34,994. $ -. $ 13,127. $</t>
+          <t>Balance at December 31, 2023 5 22,520,366 $ 2,888,720 $ 45,848 $ 73,127 $</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -19533,11 +19465,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" s="5" t="n">
-        <v>0.538771</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>-0.25452</v>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -19554,15 +19490,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L187" s="5" t="n">
+        <v>1.60421</v>
+      </c>
+      <c r="M187" s="5" t="n">
+        <v>-1.403485</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -19581,21 +19513,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>4(b))</t>
-        </is>
-      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Loss for the year -. -. -. -. -.</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>For the years ended December</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -19606,11 +19530,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" s="5" t="n">
-        <v>-0.067092</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>-0.067092</v>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -19622,20 +19550,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K188" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M188" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -19656,15 +19580,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>4(b))</t>
+          <t>Consulting fees                                          $      17,505  $                 ‐</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2015 10,700,000. $ 685,170. $ 34,994. $ 73,127. $ -. $</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Office 27,878</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -19675,11 +19603,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G189" s="5" t="n">
-        <v>0.471679</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>-0.321612</v>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -19701,10 +19633,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M189" s="5" t="n">
+        <v>0.064383</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -19725,15 +19655,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>4(b))</t>
+          <t>Consulting fees                                          $      17,505  $                 ‐</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2016 10,700,000. $ 685,170. $ 34,994. $ 73,127. $ -. $</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Professional fees 110,286</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -19744,11 +19678,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G190" s="5" t="n">
-        <v>0.394434</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>-0.398857</v>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -19770,10 +19708,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M190" s="5" t="n">
+        <v>0.057062</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -19794,24 +19730,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Property investigation                                                                                   -.            240.</t>
+          <t>Consulting fees                                          $      17,505  $                 ‐</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Transfer agent and filing fees 38,400</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E191" s="5" t="n">
-        <v>0.039599</v>
-      </c>
-      <c r="F191" s="5" t="n">
-        <v>0.031942</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -19843,10 +19783,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M191" s="5" t="n">
+        <v>0.012049</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -19867,24 +19805,24 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Property investigation                                                                                   -.            240.</t>
+          <t>Consulting fees                                          $      17,505  $                 ‐</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E192" s="5" t="n">
-        <v>0.015937</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>0.018265</v>
+          <t>Loss before other item (194,069)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -19916,10 +19854,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M192" s="5" t="n">
+        <v>-0.133494</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
@@ -19940,24 +19876,24 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Share based compensation)                                                           -.         34,994.</t>
+          <t>Interest income                                                                                          ‐                      ‐</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="n">
-        <v>0.016867</v>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>0.018926</v>
+          <t>Net and comprehensive loss $ (194,069) $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -19989,10 +19925,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M193" s="5" t="n">
+        <v>-0.133494</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -20013,24 +19947,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Share based compensation)                                                           -.         34,994.</t>
+          <t>Interest income                                                                                          ‐                      ‐</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Weighted average number of shares outstanding 22,520,366</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E194" s="5" t="n">
-        <v>-0.118103</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>-0.096648</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -20062,10 +20000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M194" s="5" t="n">
+        <v>14.629955</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -20086,20 +20022,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+          <t>Interest income                                                                                          ‐                      ‐</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2012 4,200,000. $ 310,000. $ -. $ -. $</t>
+          <t>Basic and diluted net loss per share $ (0.01) $</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" s="5" t="n">
-        <v>0.270231</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>-0.039769</v>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -20131,10 +20071,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M195" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -20155,24 +20093,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+          <t>(828,749) ‐   (133,494)     (962,243)                   (962,243)    (194,069)      (1,156,312)                                                              Deficit</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Loss for the year -. -. -. -.</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E196" s="5" t="n">
-        <v>-0.118103</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>-0.118103</v>
+          <t>(828,749) ‐   (133,494)     (962,243)                   (962,243)    (194,069)      (1,156,312)                                                              Deficit</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -20204,10 +20142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M196" s="5" t="n">
+        <v>0.073127</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -20228,20 +20164,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+          <t>‐ ‐     ‐                                                                                                                                                                                                                                                                                                                                                              financial</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2013 6,700,000. $ 499,995. $ 34,994. $ 13,127. $</t>
+          <t>‐ ‐     ‐                                                                                                                                                                                                                                                                                                                                                              financial</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" s="5" t="n">
-        <v>0.390244</v>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>-0.157872</v>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -20273,10 +20213,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M197" s="5" t="n">
+        <v>0.045848</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
@@ -20297,62 +20235,2800 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
+          <t>The</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Equity in dollars) 2021</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>The</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>The total</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M199" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Consulting fees (note 6) $ 40,580 $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>0.023253</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Office 25,250</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>0.019275</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Professional fees 43,745</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.028407</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees 22,733</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>0.017156</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Loss before other item (132,308)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>-0.088091</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Interest income 987</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss $ (131,321) $</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>-0.087031</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding 29,185,007</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>29.185007</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss per share $ (0.00) $</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Consulting fees (note 5) $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.006658</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>0.019309</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>0.035361</v>
+      </c>
+      <c r="J211" s="5" t="n">
+        <v>0.045008</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Share based compensation (note 4, 5)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>0.010854</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0.022814</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>0.024286</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>-0.091437</v>
+      </c>
+      <c r="J214" s="5" t="n">
+        <v>-0.120103</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>25.429637</v>
+      </c>
+      <c r="J216" s="5" t="n">
+        <v>31.931007</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Consulting fees $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>0.009344999999999999</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>0.0007159999999999999</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>0.000632</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.002821</v>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>0.001053</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.019824</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>0.014517</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>0.019751</v>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>0.020753</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.014826</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>0.014909</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Travel expense                                                      16,668.                       -.</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>-0.067092</v>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>-0.07724499999999999</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss per share</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss per share</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>6.152055</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>8.110958999999999</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>11.664384</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Shares          capital.           reserve.        surplus        reserve           Deficit.         Total</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2014 11,700,000. $ 745,170. $ 34,994. $ -. $ 13,127. $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>0.538771</v>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>-0.25452</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>4(b))</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Loss for the year -. -. -. -. -.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>-0.067092</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-0.067092</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>4(b))</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2015 10,700,000. $ 685,170. $ 34,994. $ 73,127. $ -. $</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>0.471679</v>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>-0.321612</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>4(b))</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2016 10,700,000. $ 685,170. $ 34,994. $ 73,127. $ -. $</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.394434</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>-0.398857</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Property investigation                                                                                   -.            240.</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>0.039599</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>0.031942</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Property investigation                                                                                   -.            240.</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>0.015937</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>0.018265</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Share based compensation)                                                           -.         34,994.</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>0.016867</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>0.018926</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Share based compensation)                                                           -.         34,994.</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>-0.118103</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-0.096648</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
           <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2012 4,200,000. $ 310,000. $ -. $ -. $</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
+        <v>0.270231</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>-0.039769</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Loss for the year -. -. -. -.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>-0.118103</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>-0.118103</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2013 6,700,000. $ 499,995. $ 34,994. $ 13,127. $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" s="5" t="n">
+        <v>0.390244</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>-0.157872</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Shares          capital.           reserve.        reserve           Deficit.         Total</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Balance, December 31, 2014 11,700,000. $ 745,170. $ 34,994. $ 13,127. $</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" s="5" t="n">
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" s="5" t="n">
         <v>0.538771</v>
       </c>
-      <c r="F198" s="5" t="n">
+      <c r="F236" s="5" t="n">
         <v>-0.25452</v>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
